--- a/data/appliances_1.xlsx
+++ b/data/appliances_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stuja\OneDrive\Dokumenter\Studie\0. Etterstudium\Eninf Oblig 1\git2\in5410_intelligent_load_scheduling\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D96B514-C233-49A4-9530-0847274CEAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E16438-6809-4F00-8185-A29077C45308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -96,10 +96,10 @@
     <t>17-31</t>
   </si>
   <si>
-    <t>19-26, 30-31</t>
-  </si>
-  <si>
     <t>duration_slots</t>
+  </si>
+  <si>
+    <t>19-26, 30-34</t>
   </si>
 </sst>
 </file>
@@ -500,7 +500,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>6</v>
@@ -620,7 +620,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="3" t="str" cm="1">
         <f t="array" ref="F4">_xlfn.LET(
@@ -641,7 +641,7 @@
   )),
   _xlfn.TEXTJOIN(", ", TRUE, _xlpm.out)
 )</f>
-        <v>77-105, 121-125</v>
+        <v>77-105, 121-137</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
